--- a/201025_Results_Cali/output/summary/merged_mod1.xlsx
+++ b/201025_Results_Cali/output/summary/merged_mod1.xlsx
@@ -1,27 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Natura/201025_Results_Cali/output/summary/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="11_90569FC58F79A8D366075C52F37BD2721A4D3402" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72E3BF7F-E75E-4F73-9F94-BCAE5CD5051E}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_82529DD58F79A8D366075C52F37BD2722A47C4FF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{259D9527-D30B-45DE-9544-DFBB98E9B87B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="543">
   <si>
     <t>Variable</t>
   </si>
@@ -32,105 +31,96 @@
     <t>Categoria</t>
   </si>
   <si>
-    <t>Hombre.x</t>
-  </si>
-  <si>
-    <t>Mujer.x</t>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
   <si>
     <t>p_value.x</t>
   </si>
   <si>
-    <t>Hombre.y</t>
-  </si>
-  <si>
-    <t>Mujer.y</t>
+    <t>Alto</t>
+  </si>
+  <si>
+    <t>Bajo</t>
+  </si>
+  <si>
+    <t>Medio</t>
   </si>
   <si>
     <t>p_value.y</t>
   </si>
   <si>
-    <t>Alto</t>
-  </si>
-  <si>
-    <t>Bajo</t>
-  </si>
-  <si>
-    <t>Medio</t>
+    <t>Auto privado</t>
+  </si>
+  <si>
+    <t>Modo activo</t>
+  </si>
+  <si>
+    <t>Moto privada</t>
+  </si>
+  <si>
+    <t>Taxi / Plataforma</t>
+  </si>
+  <si>
+    <t>Transporte informal</t>
+  </si>
+  <si>
+    <t>Transporte público</t>
   </si>
   <si>
     <t>p_value.x.x</t>
   </si>
   <si>
-    <t>Auto privado</t>
-  </si>
-  <si>
-    <t>Modo activo</t>
-  </si>
-  <si>
-    <t>Moto privada</t>
-  </si>
-  <si>
-    <t>Taxi / Plataforma</t>
-  </si>
-  <si>
-    <t>Transporte informal</t>
-  </si>
-  <si>
-    <t>Transporte público</t>
+    <t>Primaria o menos</t>
+  </si>
+  <si>
+    <t>Secundaria</t>
+  </si>
+  <si>
+    <t>Sin respuesta</t>
+  </si>
+  <si>
+    <t>Superior</t>
+  </si>
+  <si>
+    <t>Técnico / Tecnológico</t>
   </si>
   <si>
     <t>p_value.y.y</t>
   </si>
   <si>
-    <t>Primaria o menos</t>
-  </si>
-  <si>
-    <t>Secundaria</t>
-  </si>
-  <si>
-    <t>Sin respuesta</t>
-  </si>
-  <si>
-    <t>Superior</t>
-  </si>
-  <si>
-    <t>Técnico / Tecnológico</t>
+    <t>Desocupado o inactivo</t>
+  </si>
+  <si>
+    <t>Estudiante</t>
+  </si>
+  <si>
+    <t>Ocupado/a</t>
+  </si>
+  <si>
+    <t>Otro</t>
+  </si>
+  <si>
+    <t>Trabajo doméstico no remunerado</t>
   </si>
   <si>
     <t>p_value.x.x.x</t>
   </si>
   <si>
-    <t>Desocupado o inactivo</t>
-  </si>
-  <si>
-    <t>Estudiante</t>
-  </si>
-  <si>
-    <t>Ocupado/a</t>
-  </si>
-  <si>
-    <t>Otro</t>
-  </si>
-  <si>
-    <t>Trabajo doméstico no remunerado</t>
+    <t>18 - 34 años</t>
+  </si>
+  <si>
+    <t>35 - 54 años</t>
+  </si>
+  <si>
+    <t>55 - 80 años</t>
   </si>
   <si>
     <t>p_value.y.y.y</t>
   </si>
   <si>
-    <t>18 - 34 años</t>
-  </si>
-  <si>
-    <t>35 - 54 años</t>
-  </si>
-  <si>
-    <t>55 - 80 años</t>
-  </si>
-  <si>
-    <t>p_value</t>
-  </si>
-  <si>
     <t>Modulo</t>
   </si>
   <si>
@@ -1487,9 +1477,6 @@
     <t>Con qué género se identifica</t>
   </si>
   <si>
-    <t>Hombre</t>
-  </si>
-  <si>
     <t>212 (100.0%)</t>
   </si>
   <si>
@@ -1539,9 +1526,6 @@
   </si>
   <si>
     <t>75 (53.2%)</t>
-  </si>
-  <si>
-    <t>Mujer</t>
   </si>
   <si>
     <t>221 (100.0%)</t>
@@ -1728,10 +1712,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2021,36 +2001,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AK31"/>
+  <dimension ref="A1:AH31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="33" max="35" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2153,55 +2113,46 @@
       <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="B2" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="E2" t="s">
         <v>37</v>
-      </c>
-      <c r="B2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" t="s">
-        <v>40</v>
       </c>
       <c r="F2">
         <v>0.45479999999999998</v>
       </c>
       <c r="G2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" t="s">
         <v>39</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>40</v>
       </c>
-      <c r="I2">
-        <v>0.45479999999999998</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="J2">
+        <v>0.12889999999999999</v>
+      </c>
+      <c r="K2" t="s">
         <v>41</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>42</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>43</v>
-      </c>
-      <c r="M2">
-        <v>0.12889999999999999</v>
       </c>
       <c r="N2" t="s">
         <v>44</v>
@@ -2212,35 +2163,35 @@
       <c r="P2" t="s">
         <v>46</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2" t="s">
         <v>47</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>48</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" t="s">
         <v>49</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>50</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2" t="s">
         <v>51</v>
       </c>
-      <c r="W2" t="s">
-        <v>48</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>52</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>53</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
       </c>
       <c r="AA2" t="s">
         <v>54</v>
@@ -2248,73 +2199,64 @@
       <c r="AB2" t="s">
         <v>55</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="s">
         <v>56</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="s">
         <v>57</v>
       </c>
-      <c r="AE2" t="s">
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
         <v>58</v>
       </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="s">
+      <c r="E3" t="s">
         <v>59</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" t="s">
-        <v>62</v>
       </c>
       <c r="F3">
         <v>0.45479999999999998</v>
       </c>
       <c r="G3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H3" t="s">
         <v>61</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>62</v>
       </c>
-      <c r="I3">
-        <v>0.45479999999999998</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="J3">
+        <v>0.12889999999999999</v>
+      </c>
+      <c r="K3" t="s">
         <v>63</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>64</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>65</v>
-      </c>
-      <c r="M3">
-        <v>0.12889999999999999</v>
       </c>
       <c r="N3" t="s">
         <v>66</v>
@@ -2325,109 +2267,100 @@
       <c r="P3" t="s">
         <v>68</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3" t="s">
         <v>69</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>70</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" t="s">
         <v>71</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>72</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3" t="s">
         <v>73</v>
       </c>
-      <c r="W3" t="s">
-        <v>48</v>
-      </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
         <v>74</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Z3" t="s">
         <v>75</v>
       </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
       <c r="AA3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB3" t="s">
         <v>76</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE3" t="s">
         <v>77</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AF3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
         <v>78</v>
       </c>
-      <c r="AD3" t="s">
-        <v>57</v>
-      </c>
-      <c r="AE3" t="s">
+      <c r="E4" t="s">
         <v>79</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" t="s">
-        <v>82</v>
       </c>
       <c r="F4">
         <v>0.45479999999999998</v>
       </c>
       <c r="G4" t="s">
+        <v>80</v>
+      </c>
+      <c r="H4" t="s">
         <v>81</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>82</v>
       </c>
-      <c r="I4">
-        <v>0.45479999999999998</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="J4">
+        <v>0.12889999999999999</v>
+      </c>
+      <c r="K4" t="s">
         <v>83</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>84</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>85</v>
-      </c>
-      <c r="M4">
-        <v>0.12889999999999999</v>
       </c>
       <c r="N4" t="s">
         <v>86</v>
@@ -2438,17 +2371,17 @@
       <c r="P4" t="s">
         <v>88</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4" t="s">
         <v>89</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>90</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>91</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
       </c>
       <c r="U4" t="s">
         <v>92</v>
@@ -2456,91 +2389,82 @@
       <c r="V4" t="s">
         <v>93</v>
       </c>
-      <c r="W4" t="s">
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4" t="s">
         <v>94</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z4" t="s">
         <v>95</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="AA4" t="s">
         <v>96</v>
       </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>97</v>
       </c>
-      <c r="AB4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC4" t="s">
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF4" t="s">
         <v>98</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>99</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="B5" t="s">
         <v>100</v>
       </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI4" t="s">
+      <c r="C5" t="s">
         <v>101</v>
       </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="D5" t="s">
         <v>102</v>
       </c>
-      <c r="B5" t="s">
+      <c r="E5" t="s">
         <v>103</v>
-      </c>
-      <c r="C5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E5" t="s">
-        <v>106</v>
       </c>
       <c r="F5">
         <v>0.60819999999999996</v>
       </c>
       <c r="G5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H5" t="s">
         <v>105</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>106</v>
       </c>
-      <c r="I5">
-        <v>0.82599999999999996</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="J5">
+        <v>0.35970000000000002</v>
+      </c>
+      <c r="K5" t="s">
         <v>107</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>108</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>109</v>
-      </c>
-      <c r="M5">
-        <v>0.35970000000000002</v>
       </c>
       <c r="N5" t="s">
         <v>110</v>
@@ -2551,35 +2475,35 @@
       <c r="P5" t="s">
         <v>112</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="Q5">
+        <v>0.47670000000000001</v>
+      </c>
+      <c r="R5" t="s">
         <v>113</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>114</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
+        <v>91</v>
+      </c>
+      <c r="U5" t="s">
         <v>115</v>
       </c>
-      <c r="T5">
-        <v>0.47670000000000001</v>
-      </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
         <v>116</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W5">
+        <v>0.16470000000000001</v>
+      </c>
+      <c r="X5" t="s">
         <v>117</v>
       </c>
-      <c r="W5" t="s">
-        <v>94</v>
-      </c>
-      <c r="X5" t="s">
+      <c r="Y5" t="s">
         <v>118</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="Z5" t="s">
         <v>119</v>
-      </c>
-      <c r="Z5">
-        <v>0.16470000000000001</v>
       </c>
       <c r="AA5" t="s">
         <v>120</v>
@@ -2587,225 +2511,207 @@
       <c r="AB5" t="s">
         <v>121</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AC5">
+        <v>0.47339999999999999</v>
+      </c>
+      <c r="AD5" t="s">
         <v>122</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AE5" t="s">
         <v>123</v>
       </c>
-      <c r="AE5" t="s">
+      <c r="AF5" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG5">
+        <v>1.15E-2</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" t="s">
         <v>124</v>
       </c>
-      <c r="AF5">
-        <v>0.47339999999999999</v>
-      </c>
-      <c r="AG5" t="s">
+      <c r="D6" t="s">
         <v>125</v>
       </c>
-      <c r="AH5" t="s">
+      <c r="E6" t="s">
         <v>126</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>101</v>
-      </c>
-      <c r="AJ5">
-        <v>1.15E-2</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" t="s">
-        <v>127</v>
-      </c>
-      <c r="D6" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6" t="s">
-        <v>129</v>
       </c>
       <c r="F6">
         <v>0.60819999999999996</v>
       </c>
       <c r="G6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H6" t="s">
         <v>128</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>129</v>
       </c>
-      <c r="I6">
-        <v>0.82599999999999996</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="J6">
+        <v>0.35970000000000002</v>
+      </c>
+      <c r="K6" t="s">
         <v>130</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M6" t="s">
         <v>131</v>
       </c>
-      <c r="L6" t="s">
+      <c r="N6" t="s">
         <v>132</v>
       </c>
-      <c r="M6">
-        <v>0.35970000000000002</v>
-      </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
+        <v>45</v>
+      </c>
+      <c r="P6" t="s">
         <v>133</v>
       </c>
-      <c r="O6" t="s">
-        <v>48</v>
-      </c>
-      <c r="P6" t="s">
+      <c r="Q6">
+        <v>0.47670000000000001</v>
+      </c>
+      <c r="R6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S6" t="s">
         <v>134</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="T6" t="s">
+        <v>45</v>
+      </c>
+      <c r="U6" t="s">
+        <v>45</v>
+      </c>
+      <c r="V6" t="s">
         <v>135</v>
       </c>
-      <c r="R6" t="s">
-        <v>48</v>
-      </c>
-      <c r="S6" t="s">
+      <c r="W6">
+        <v>0.16470000000000001</v>
+      </c>
+      <c r="X6" t="s">
         <v>136</v>
       </c>
-      <c r="T6">
-        <v>0.47670000000000001</v>
-      </c>
-      <c r="U6" t="s">
-        <v>48</v>
-      </c>
-      <c r="V6" t="s">
+      <c r="Y6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z6" t="s">
         <v>137</v>
       </c>
-      <c r="W6" t="s">
-        <v>48</v>
-      </c>
-      <c r="X6" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y6" t="s">
+      <c r="AA6" t="s">
         <v>138</v>
       </c>
-      <c r="Z6">
-        <v>0.16470000000000001</v>
-      </c>
-      <c r="AA6" t="s">
+      <c r="AB6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC6">
+        <v>0.47339999999999999</v>
+      </c>
+      <c r="AD6" t="s">
         <v>139</v>
       </c>
-      <c r="AB6" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC6" t="s">
+      <c r="AE6" t="s">
         <v>140</v>
       </c>
-      <c r="AD6" t="s">
+      <c r="AF6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG6">
+        <v>1.15E-2</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>141</v>
       </c>
-      <c r="AE6" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF6">
-        <v>0.47339999999999999</v>
-      </c>
-      <c r="AG6" t="s">
+      <c r="B7" t="s">
         <v>142</v>
       </c>
-      <c r="AH6" t="s">
+      <c r="C7" t="s">
         <v>143</v>
       </c>
-      <c r="AI6" t="s">
-        <v>48</v>
-      </c>
-      <c r="AJ6">
-        <v>1.15E-2</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="D7" t="s">
         <v>144</v>
       </c>
-      <c r="B7" t="s">
+      <c r="E7" t="s">
         <v>145</v>
-      </c>
-      <c r="C7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E7" t="s">
-        <v>148</v>
       </c>
       <c r="F7">
         <v>0.39400000000000002</v>
       </c>
       <c r="G7" t="s">
+        <v>146</v>
+      </c>
+      <c r="H7" t="s">
         <v>147</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>148</v>
       </c>
-      <c r="I7">
-        <v>0.39400000000000002</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="J7">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="K7" t="s">
         <v>149</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>150</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>151</v>
-      </c>
-      <c r="M7">
-        <v>1.1000000000000001E-3</v>
       </c>
       <c r="N7" t="s">
         <v>152</v>
       </c>
       <c r="O7" t="s">
+        <v>67</v>
+      </c>
+      <c r="P7" t="s">
         <v>153</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7">
+        <v>6.3E-3</v>
+      </c>
+      <c r="R7" t="s">
         <v>154</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="S7" t="s">
         <v>155</v>
       </c>
-      <c r="R7" t="s">
-        <v>70</v>
-      </c>
-      <c r="S7" t="s">
+      <c r="T7" t="s">
+        <v>91</v>
+      </c>
+      <c r="U7" t="s">
         <v>156</v>
       </c>
-      <c r="T7">
-        <v>6.3E-3</v>
-      </c>
-      <c r="U7" t="s">
+      <c r="V7" t="s">
         <v>157</v>
       </c>
-      <c r="V7" t="s">
+      <c r="W7">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="X7" t="s">
         <v>158</v>
       </c>
-      <c r="W7" t="s">
-        <v>94</v>
-      </c>
-      <c r="X7" t="s">
+      <c r="Y7" t="s">
         <v>159</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="Z7" t="s">
         <v>160</v>
-      </c>
-      <c r="Z7">
-        <v>0.28799999999999998</v>
       </c>
       <c r="AA7" t="s">
         <v>161</v>
@@ -2813,112 +2719,103 @@
       <c r="AB7" t="s">
         <v>162</v>
       </c>
-      <c r="AC7" t="s">
+      <c r="AC7">
+        <v>0.9607</v>
+      </c>
+      <c r="AD7" t="s">
         <v>163</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AE7" t="s">
         <v>164</v>
       </c>
-      <c r="AE7" t="s">
+      <c r="AF7" t="s">
         <v>165</v>
       </c>
-      <c r="AF7">
-        <v>0.9607</v>
-      </c>
-      <c r="AG7" t="s">
+      <c r="AG7">
+        <v>0.42720000000000002</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" t="s">
         <v>166</v>
       </c>
-      <c r="AH7" t="s">
+      <c r="D8" t="s">
         <v>167</v>
       </c>
-      <c r="AI7" t="s">
+      <c r="E8" t="s">
         <v>168</v>
-      </c>
-      <c r="AJ7">
-        <v>0.42720000000000002</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>144</v>
-      </c>
-      <c r="B8" t="s">
-        <v>145</v>
-      </c>
-      <c r="C8" t="s">
-        <v>169</v>
-      </c>
-      <c r="D8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E8" t="s">
-        <v>171</v>
       </c>
       <c r="F8">
         <v>0.39400000000000002</v>
       </c>
       <c r="G8" t="s">
+        <v>169</v>
+      </c>
+      <c r="H8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" t="s">
         <v>170</v>
       </c>
-      <c r="H8" t="s">
+      <c r="J8">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="K8" t="s">
         <v>171</v>
       </c>
-      <c r="I8">
-        <v>0.39400000000000002</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="L8" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8" t="s">
         <v>172</v>
       </c>
-      <c r="K8" t="s">
-        <v>42</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="N8" t="s">
         <v>173</v>
       </c>
-      <c r="M8">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="N8" t="s">
+      <c r="O8" t="s">
+        <v>67</v>
+      </c>
+      <c r="P8" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q8">
+        <v>6.3E-3</v>
+      </c>
+      <c r="R8" t="s">
         <v>174</v>
       </c>
-      <c r="O8" t="s">
-        <v>45</v>
-      </c>
-      <c r="P8" t="s">
+      <c r="S8" t="s">
         <v>175</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="T8" t="s">
+        <v>45</v>
+      </c>
+      <c r="U8" t="s">
         <v>176</v>
       </c>
-      <c r="R8" t="s">
-        <v>70</v>
-      </c>
-      <c r="S8" t="s">
-        <v>71</v>
-      </c>
-      <c r="T8">
-        <v>6.3E-3</v>
-      </c>
-      <c r="U8" t="s">
+      <c r="V8" t="s">
         <v>177</v>
       </c>
-      <c r="V8" t="s">
+      <c r="W8">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="X8" t="s">
         <v>178</v>
       </c>
-      <c r="W8" t="s">
-        <v>48</v>
-      </c>
-      <c r="X8" t="s">
+      <c r="Y8" t="s">
         <v>179</v>
       </c>
-      <c r="Y8" t="s">
+      <c r="Z8" t="s">
         <v>180</v>
-      </c>
-      <c r="Z8">
-        <v>0.28799999999999998</v>
       </c>
       <c r="AA8" t="s">
         <v>181</v>
@@ -2926,73 +2823,64 @@
       <c r="AB8" t="s">
         <v>182</v>
       </c>
-      <c r="AC8" t="s">
+      <c r="AC8">
+        <v>0.9607</v>
+      </c>
+      <c r="AD8" t="s">
         <v>183</v>
       </c>
-      <c r="AD8" t="s">
+      <c r="AE8" t="s">
         <v>184</v>
       </c>
-      <c r="AE8" t="s">
+      <c r="AF8" t="s">
         <v>185</v>
       </c>
-      <c r="AF8">
-        <v>0.9607</v>
-      </c>
-      <c r="AG8" t="s">
+      <c r="AG8">
+        <v>0.42720000000000002</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>141</v>
+      </c>
+      <c r="B9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C9" t="s">
         <v>186</v>
       </c>
-      <c r="AH8" t="s">
+      <c r="D9" t="s">
         <v>187</v>
       </c>
-      <c r="AI8" t="s">
+      <c r="E9" t="s">
         <v>188</v>
-      </c>
-      <c r="AJ8">
-        <v>0.42720000000000002</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>144</v>
-      </c>
-      <c r="B9" t="s">
-        <v>145</v>
-      </c>
-      <c r="C9" t="s">
-        <v>189</v>
-      </c>
-      <c r="D9" t="s">
-        <v>190</v>
-      </c>
-      <c r="E9" t="s">
-        <v>191</v>
       </c>
       <c r="F9">
         <v>0.39400000000000002</v>
       </c>
       <c r="G9" t="s">
+        <v>127</v>
+      </c>
+      <c r="H9" t="s">
+        <v>189</v>
+      </c>
+      <c r="I9" t="s">
         <v>190</v>
       </c>
-      <c r="H9" t="s">
+      <c r="J9">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="K9" t="s">
         <v>191</v>
       </c>
-      <c r="I9">
-        <v>0.39400000000000002</v>
-      </c>
-      <c r="J9" t="s">
-        <v>130</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>192</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>193</v>
-      </c>
-      <c r="M9">
-        <v>1.1000000000000001E-3</v>
       </c>
       <c r="N9" t="s">
         <v>194</v>
@@ -3003,2143 +2891,1972 @@
       <c r="P9" t="s">
         <v>196</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="Q9">
+        <v>6.3E-3</v>
+      </c>
+      <c r="R9" t="s">
         <v>197</v>
       </c>
-      <c r="R9" t="s">
+      <c r="S9" t="s">
         <v>198</v>
       </c>
-      <c r="S9" t="s">
+      <c r="T9" t="s">
+        <v>45</v>
+      </c>
+      <c r="U9" t="s">
         <v>199</v>
       </c>
-      <c r="T9">
-        <v>6.3E-3</v>
-      </c>
-      <c r="U9" t="s">
+      <c r="V9" t="s">
         <v>200</v>
       </c>
-      <c r="V9" t="s">
+      <c r="W9">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="X9" t="s">
         <v>201</v>
       </c>
-      <c r="W9" t="s">
-        <v>48</v>
-      </c>
-      <c r="X9" t="s">
+      <c r="Y9" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z9" t="s">
         <v>202</v>
       </c>
-      <c r="Y9" t="s">
+      <c r="AA9" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB9" t="s">
         <v>203</v>
       </c>
-      <c r="Z9">
-        <v>0.28799999999999998</v>
-      </c>
-      <c r="AA9" t="s">
+      <c r="AC9">
+        <v>0.9607</v>
+      </c>
+      <c r="AD9" t="s">
         <v>204</v>
       </c>
-      <c r="AB9" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC9" t="s">
+      <c r="AE9" t="s">
         <v>205</v>
       </c>
-      <c r="AD9" t="s">
-        <v>184</v>
-      </c>
-      <c r="AE9" t="s">
+      <c r="AF9" t="s">
         <v>206</v>
       </c>
-      <c r="AF9">
-        <v>0.9607</v>
-      </c>
-      <c r="AG9" t="s">
+      <c r="AG9">
+        <v>0.42720000000000002</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
         <v>207</v>
       </c>
-      <c r="AH9" t="s">
-        <v>208</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>209</v>
-      </c>
-      <c r="AJ9">
-        <v>0.42720000000000002</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>144</v>
-      </c>
-      <c r="B10" t="s">
-        <v>145</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" t="s">
-        <v>210</v>
-      </c>
       <c r="E10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F10">
         <v>0.39400000000000002</v>
       </c>
       <c r="G10" t="s">
+        <v>127</v>
+      </c>
+      <c r="H10" t="s">
+        <v>208</v>
+      </c>
+      <c r="I10" t="s">
+        <v>209</v>
+      </c>
+      <c r="J10">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="K10" t="s">
         <v>210</v>
       </c>
-      <c r="H10" t="s">
-        <v>129</v>
-      </c>
-      <c r="I10">
-        <v>0.39400000000000002</v>
-      </c>
-      <c r="J10" t="s">
-        <v>130</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M10" t="s">
         <v>211</v>
       </c>
-      <c r="L10" t="s">
+      <c r="N10" t="s">
+        <v>194</v>
+      </c>
+      <c r="O10" t="s">
+        <v>45</v>
+      </c>
+      <c r="P10" t="s">
         <v>212</v>
       </c>
-      <c r="M10">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="N10" t="s">
+      <c r="Q10">
+        <v>6.3E-3</v>
+      </c>
+      <c r="R10" t="s">
+        <v>47</v>
+      </c>
+      <c r="S10" t="s">
         <v>213</v>
       </c>
-      <c r="O10" t="s">
-        <v>48</v>
-      </c>
-      <c r="P10" t="s">
+      <c r="T10" t="s">
+        <v>45</v>
+      </c>
+      <c r="U10" t="s">
         <v>214</v>
       </c>
-      <c r="Q10" t="s">
-        <v>197</v>
-      </c>
-      <c r="R10" t="s">
-        <v>48</v>
-      </c>
-      <c r="S10" t="s">
+      <c r="V10" t="s">
         <v>215</v>
       </c>
-      <c r="T10">
-        <v>6.3E-3</v>
-      </c>
-      <c r="U10" t="s">
-        <v>50</v>
-      </c>
-      <c r="V10" t="s">
+      <c r="W10">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="X10" t="s">
         <v>216</v>
       </c>
-      <c r="W10" t="s">
-        <v>48</v>
-      </c>
-      <c r="X10" t="s">
+      <c r="Y10" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z10" t="s">
         <v>217</v>
       </c>
-      <c r="Y10" t="s">
+      <c r="AA10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB10" t="s">
         <v>218</v>
       </c>
-      <c r="Z10">
-        <v>0.28799999999999998</v>
-      </c>
-      <c r="AA10" t="s">
+      <c r="AC10">
+        <v>0.9607</v>
+      </c>
+      <c r="AD10" t="s">
         <v>219</v>
       </c>
-      <c r="AB10" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC10" t="s">
+      <c r="AE10" t="s">
         <v>220</v>
       </c>
-      <c r="AD10" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE10" t="s">
+      <c r="AF10" t="s">
         <v>221</v>
       </c>
-      <c r="AF10">
-        <v>0.9607</v>
-      </c>
-      <c r="AG10" t="s">
+      <c r="AG10">
+        <v>0.42720000000000002</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>222</v>
       </c>
-      <c r="AH10" t="s">
+      <c r="B11" t="s">
         <v>223</v>
       </c>
-      <c r="AI10" t="s">
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
         <v>224</v>
       </c>
-      <c r="AJ10">
-        <v>0.42720000000000002</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="E11" t="s">
         <v>225</v>
-      </c>
-      <c r="B11" t="s">
-        <v>226</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" t="s">
-        <v>227</v>
-      </c>
-      <c r="E11" t="s">
-        <v>228</v>
       </c>
       <c r="F11">
         <v>0.82289999999999996</v>
       </c>
       <c r="G11" t="s">
+        <v>226</v>
+      </c>
+      <c r="H11" t="s">
         <v>227</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>228</v>
       </c>
-      <c r="I11">
-        <v>0.82289999999999996</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>191</v>
+      </c>
+      <c r="L11" t="s">
         <v>229</v>
       </c>
-      <c r="K11" t="s">
+      <c r="M11" t="s">
         <v>230</v>
       </c>
-      <c r="L11" t="s">
+      <c r="N11" t="s">
+        <v>44</v>
+      </c>
+      <c r="O11" t="s">
         <v>231</v>
       </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>194</v>
-      </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>232</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11" t="s">
+        <v>113</v>
+      </c>
+      <c r="S11" t="s">
+        <v>45</v>
+      </c>
+      <c r="T11" t="s">
+        <v>45</v>
+      </c>
+      <c r="U11" t="s">
+        <v>45</v>
+      </c>
+      <c r="V11" t="s">
+        <v>45</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11" t="s">
         <v>233</v>
       </c>
-      <c r="Q11" t="s">
-        <v>47</v>
-      </c>
-      <c r="R11" t="s">
+      <c r="Y11" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z11" t="s">
         <v>234</v>
       </c>
-      <c r="S11" t="s">
+      <c r="AA11" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB11" t="s">
         <v>235</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11" t="s">
-        <v>116</v>
-      </c>
-      <c r="V11" t="s">
-        <v>48</v>
-      </c>
-      <c r="W11" t="s">
-        <v>48</v>
-      </c>
-      <c r="X11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="s">
+      <c r="AC11">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="AD11" t="s">
         <v>236</v>
       </c>
-      <c r="AB11" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC11" t="s">
+      <c r="AE11" t="s">
         <v>237</v>
       </c>
-      <c r="AD11" t="s">
-        <v>184</v>
-      </c>
-      <c r="AE11" t="s">
+      <c r="AF11" t="s">
         <v>238</v>
       </c>
-      <c r="AF11">
-        <v>1.0800000000000001E-2</v>
-      </c>
-      <c r="AG11" t="s">
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>222</v>
+      </c>
+      <c r="B12" t="s">
+        <v>223</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
         <v>239</v>
       </c>
-      <c r="AH11" t="s">
+      <c r="E12" t="s">
         <v>240</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>241</v>
-      </c>
-      <c r="AJ11">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>225</v>
-      </c>
-      <c r="B12" t="s">
-        <v>226</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" t="s">
-        <v>242</v>
-      </c>
-      <c r="E12" t="s">
-        <v>243</v>
       </c>
       <c r="F12">
         <v>0.82289999999999996</v>
       </c>
       <c r="G12" t="s">
+        <v>241</v>
+      </c>
+      <c r="H12" t="s">
         <v>242</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>243</v>
       </c>
-      <c r="I12">
-        <v>0.82289999999999996</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" t="s">
         <v>244</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
         <v>245</v>
       </c>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
         <v>246</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
       </c>
       <c r="N12" t="s">
         <v>247</v>
       </c>
       <c r="O12" t="s">
+        <v>45</v>
+      </c>
+      <c r="P12" t="s">
         <v>248</v>
       </c>
-      <c r="P12" t="s">
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12" t="s">
+        <v>45</v>
+      </c>
+      <c r="S12" t="s">
         <v>249</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="T12" t="s">
+        <v>45</v>
+      </c>
+      <c r="U12" t="s">
+        <v>45</v>
+      </c>
+      <c r="V12" t="s">
+        <v>45</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12" t="s">
         <v>250</v>
       </c>
-      <c r="R12" t="s">
-        <v>48</v>
-      </c>
-      <c r="S12" t="s">
+      <c r="Y12" t="s">
         <v>251</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12" t="s">
-        <v>48</v>
-      </c>
-      <c r="V12" t="s">
+      <c r="Z12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA12" t="s">
         <v>252</v>
       </c>
-      <c r="W12" t="s">
-        <v>48</v>
-      </c>
-      <c r="X12" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="s">
+      <c r="AB12" t="s">
         <v>253</v>
       </c>
-      <c r="AB12" t="s">
+      <c r="AC12">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="AD12" t="s">
         <v>254</v>
       </c>
-      <c r="AC12" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD12" t="s">
+      <c r="AE12" t="s">
         <v>255</v>
       </c>
-      <c r="AE12" t="s">
+      <c r="AF12" t="s">
         <v>256</v>
       </c>
-      <c r="AF12">
-        <v>1.0800000000000001E-2</v>
-      </c>
-      <c r="AG12" t="s">
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
         <v>257</v>
       </c>
-      <c r="AH12" t="s">
-        <v>258</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>259</v>
-      </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>225</v>
-      </c>
-      <c r="B13" t="s">
-        <v>226</v>
-      </c>
-      <c r="C13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" t="s">
-        <v>260</v>
-      </c>
       <c r="E13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F13">
         <v>0.82289999999999996</v>
       </c>
       <c r="G13" t="s">
+        <v>258</v>
+      </c>
+      <c r="H13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
+        <v>45</v>
+      </c>
+      <c r="L13" t="s">
+        <v>259</v>
+      </c>
+      <c r="M13" t="s">
+        <v>45</v>
+      </c>
+      <c r="N13" t="s">
+        <v>45</v>
+      </c>
+      <c r="O13" t="s">
+        <v>45</v>
+      </c>
+      <c r="P13" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13" t="s">
+        <v>45</v>
+      </c>
+      <c r="S13" t="s">
+        <v>45</v>
+      </c>
+      <c r="T13" t="s">
+        <v>91</v>
+      </c>
+      <c r="U13" t="s">
+        <v>45</v>
+      </c>
+      <c r="V13" t="s">
+        <v>45</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z13" t="s">
         <v>260</v>
       </c>
-      <c r="H13" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13">
-        <v>0.82289999999999996</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="AA13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC13">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF13" t="s">
         <v>261</v>
       </c>
-      <c r="K13" t="s">
-        <v>48</v>
-      </c>
-      <c r="L13" t="s">
-        <v>48</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>48</v>
-      </c>
-      <c r="O13" t="s">
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>222</v>
+      </c>
+      <c r="B14" t="s">
+        <v>223</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
         <v>262</v>
       </c>
-      <c r="P13" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>48</v>
-      </c>
-      <c r="R13" t="s">
-        <v>48</v>
-      </c>
-      <c r="S13" t="s">
-        <v>48</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13" t="s">
-        <v>48</v>
-      </c>
-      <c r="V13" t="s">
-        <v>48</v>
-      </c>
-      <c r="W13" t="s">
-        <v>94</v>
-      </c>
-      <c r="X13" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC13" t="s">
+      <c r="E14" t="s">
         <v>263</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF13">
-        <v>1.0800000000000001E-2</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>48</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>264</v>
-      </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>225</v>
-      </c>
-      <c r="B14" t="s">
-        <v>226</v>
-      </c>
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" t="s">
-        <v>265</v>
-      </c>
-      <c r="E14" t="s">
-        <v>266</v>
       </c>
       <c r="F14">
         <v>0.82289999999999996</v>
       </c>
       <c r="G14" t="s">
+        <v>264</v>
+      </c>
+      <c r="H14" t="s">
+        <v>220</v>
+      </c>
+      <c r="I14" t="s">
+        <v>190</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
         <v>265</v>
       </c>
-      <c r="H14" t="s">
+      <c r="L14" t="s">
         <v>266</v>
       </c>
-      <c r="I14">
-        <v>0.82289999999999996</v>
-      </c>
-      <c r="J14" t="s">
+      <c r="M14" t="s">
+        <v>204</v>
+      </c>
+      <c r="N14" t="s">
         <v>267</v>
       </c>
-      <c r="K14" t="s">
+      <c r="O14" t="s">
+        <v>45</v>
+      </c>
+      <c r="P14" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14" t="s">
+        <v>45</v>
+      </c>
+      <c r="S14" t="s">
+        <v>45</v>
+      </c>
+      <c r="T14" t="s">
+        <v>45</v>
+      </c>
+      <c r="U14" t="s">
+        <v>115</v>
+      </c>
+      <c r="V14" t="s">
+        <v>45</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14" t="s">
+        <v>269</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>270</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>271</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC14">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>272</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>273</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>274</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>222</v>
+      </c>
+      <c r="B15" t="s">
         <v>223</v>
       </c>
-      <c r="L14" t="s">
-        <v>193</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14" t="s">
-        <v>268</v>
-      </c>
-      <c r="O14" t="s">
-        <v>269</v>
-      </c>
-      <c r="P14" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>270</v>
-      </c>
-      <c r="R14" t="s">
-        <v>48</v>
-      </c>
-      <c r="S14" t="s">
-        <v>271</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14" t="s">
-        <v>48</v>
-      </c>
-      <c r="V14" t="s">
-        <v>48</v>
-      </c>
-      <c r="W14" t="s">
-        <v>48</v>
-      </c>
-      <c r="X14" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>272</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>273</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>274</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>184</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>58</v>
-      </c>
-      <c r="AF14">
-        <v>1.0800000000000001E-2</v>
-      </c>
-      <c r="AG14" t="s">
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" t="s">
         <v>275</v>
       </c>
-      <c r="AH14" t="s">
+      <c r="E15" t="s">
         <v>276</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>277</v>
-      </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>225</v>
-      </c>
-      <c r="B15" t="s">
-        <v>226</v>
-      </c>
-      <c r="C15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" t="s">
-        <v>278</v>
-      </c>
-      <c r="E15" t="s">
-        <v>279</v>
       </c>
       <c r="F15">
         <v>0.82289999999999996</v>
       </c>
       <c r="G15" t="s">
+        <v>277</v>
+      </c>
+      <c r="H15" t="s">
         <v>278</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>279</v>
       </c>
-      <c r="I15">
-        <v>0.82289999999999996</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="s">
         <v>280</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
+        <v>192</v>
+      </c>
+      <c r="M15" t="s">
         <v>281</v>
       </c>
-      <c r="L15" t="s">
+      <c r="N15" t="s">
         <v>282</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>283</v>
       </c>
       <c r="O15" t="s">
         <v>195</v>
       </c>
       <c r="P15" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15" t="s">
+        <v>45</v>
+      </c>
+      <c r="S15" t="s">
+        <v>45</v>
+      </c>
+      <c r="T15" t="s">
+        <v>45</v>
+      </c>
+      <c r="U15" t="s">
+        <v>45</v>
+      </c>
+      <c r="V15" t="s">
         <v>284</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y15" t="s">
         <v>285</v>
       </c>
-      <c r="R15" t="s">
-        <v>198</v>
-      </c>
-      <c r="S15" t="s">
+      <c r="Z15" t="s">
         <v>286</v>
       </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15" t="s">
-        <v>48</v>
-      </c>
-      <c r="V15" t="s">
-        <v>48</v>
-      </c>
-      <c r="W15" t="s">
-        <v>48</v>
-      </c>
-      <c r="X15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y15" t="s">
+      <c r="AA15" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC15">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="AD15" t="s">
         <v>287</v>
       </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB15" t="s">
+      <c r="AE15" t="s">
+        <v>227</v>
+      </c>
+      <c r="AF15" t="s">
         <v>288</v>
       </c>
-      <c r="AC15" t="s">
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>289</v>
       </c>
-      <c r="AD15" t="s">
-        <v>141</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>58</v>
-      </c>
-      <c r="AF15">
+      <c r="B16" t="s">
+        <v>290</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
+        <v>291</v>
+      </c>
+      <c r="E16" t="s">
+        <v>292</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
+        <v>293</v>
+      </c>
+      <c r="H16" t="s">
+        <v>294</v>
+      </c>
+      <c r="I16" t="s">
+        <v>295</v>
+      </c>
+      <c r="J16">
+        <v>0.34410000000000002</v>
+      </c>
+      <c r="K16" t="s">
+        <v>296</v>
+      </c>
+      <c r="L16" t="s">
+        <v>297</v>
+      </c>
+      <c r="M16" t="s">
+        <v>219</v>
+      </c>
+      <c r="N16" t="s">
+        <v>282</v>
+      </c>
+      <c r="O16" t="s">
+        <v>45</v>
+      </c>
+      <c r="P16" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q16">
+        <v>1.9E-3</v>
+      </c>
+      <c r="R16" t="s">
+        <v>299</v>
+      </c>
+      <c r="S16" t="s">
+        <v>300</v>
+      </c>
+      <c r="T16" t="s">
+        <v>45</v>
+      </c>
+      <c r="U16" t="s">
+        <v>301</v>
+      </c>
+      <c r="V16" t="s">
+        <v>302</v>
+      </c>
+      <c r="W16">
         <v>1.0800000000000001E-2</v>
       </c>
-      <c r="AG15" t="s">
+      <c r="X16" t="s">
+        <v>303</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>304</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>220</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>305</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>289</v>
+      </c>
+      <c r="B17" t="s">
         <v>290</v>
       </c>
-      <c r="AH15" t="s">
-        <v>230</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>291</v>
-      </c>
-      <c r="AJ15">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="s">
-        <v>60</v>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" t="s">
+        <v>306</v>
+      </c>
+      <c r="E17" t="s">
+        <v>307</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17" t="s">
+        <v>308</v>
+      </c>
+      <c r="H17" t="s">
+        <v>140</v>
+      </c>
+      <c r="I17" t="s">
+        <v>309</v>
+      </c>
+      <c r="J17">
+        <v>0.34410000000000002</v>
+      </c>
+      <c r="K17" t="s">
+        <v>210</v>
+      </c>
+      <c r="L17" t="s">
+        <v>259</v>
+      </c>
+      <c r="M17" t="s">
+        <v>310</v>
+      </c>
+      <c r="N17" t="s">
+        <v>311</v>
+      </c>
+      <c r="O17" t="s">
+        <v>45</v>
+      </c>
+      <c r="P17" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q17">
+        <v>1.9E-3</v>
+      </c>
+      <c r="R17" t="s">
+        <v>45</v>
+      </c>
+      <c r="S17" t="s">
+        <v>313</v>
+      </c>
+      <c r="T17" t="s">
+        <v>45</v>
+      </c>
+      <c r="U17" t="s">
+        <v>314</v>
+      </c>
+      <c r="V17" t="s">
+        <v>315</v>
+      </c>
+      <c r="W17">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="X17" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>316</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>292</v>
-      </c>
-      <c r="B16" t="s">
-        <v>293</v>
-      </c>
-      <c r="C16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" t="s">
-        <v>294</v>
-      </c>
-      <c r="E16" t="s">
-        <v>295</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16" t="s">
-        <v>294</v>
-      </c>
-      <c r="H16" t="s">
-        <v>295</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16" t="s">
-        <v>296</v>
-      </c>
-      <c r="K16" t="s">
-        <v>297</v>
-      </c>
-      <c r="L16" t="s">
-        <v>298</v>
-      </c>
-      <c r="M16">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>289</v>
+      </c>
+      <c r="B18" t="s">
+        <v>290</v>
+      </c>
+      <c r="C18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" t="s">
+        <v>317</v>
+      </c>
+      <c r="E18" t="s">
+        <v>318</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
+        <v>319</v>
+      </c>
+      <c r="H18" t="s">
+        <v>320</v>
+      </c>
+      <c r="I18" t="s">
+        <v>321</v>
+      </c>
+      <c r="J18">
         <v>0.34410000000000002</v>
       </c>
-      <c r="N16" t="s">
-        <v>299</v>
-      </c>
-      <c r="O16" t="s">
-        <v>300</v>
-      </c>
-      <c r="P16" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>285</v>
-      </c>
-      <c r="R16" t="s">
-        <v>48</v>
-      </c>
-      <c r="S16" t="s">
-        <v>301</v>
-      </c>
-      <c r="T16">
-        <v>1.9E-3</v>
-      </c>
-      <c r="U16" t="s">
-        <v>302</v>
-      </c>
-      <c r="V16" t="s">
-        <v>303</v>
-      </c>
-      <c r="W16" t="s">
-        <v>48</v>
-      </c>
-      <c r="X16" t="s">
-        <v>304</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>305</v>
-      </c>
-      <c r="Z16">
-        <v>1.0800000000000001E-2</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE16" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>307</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>223</v>
-      </c>
-      <c r="AI16" t="s">
-        <v>308</v>
-      </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>292</v>
-      </c>
-      <c r="B17" t="s">
-        <v>293</v>
-      </c>
-      <c r="C17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" t="s">
-        <v>309</v>
-      </c>
-      <c r="E17" t="s">
-        <v>310</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17" t="s">
-        <v>309</v>
-      </c>
-      <c r="H17" t="s">
-        <v>310</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17" t="s">
-        <v>311</v>
-      </c>
-      <c r="K17" t="s">
-        <v>143</v>
-      </c>
-      <c r="L17" t="s">
-        <v>312</v>
-      </c>
-      <c r="M17">
-        <v>0.34410000000000002</v>
-      </c>
-      <c r="N17" t="s">
-        <v>213</v>
-      </c>
-      <c r="O17" t="s">
-        <v>262</v>
-      </c>
-      <c r="P17" t="s">
-        <v>313</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>314</v>
-      </c>
-      <c r="R17" t="s">
-        <v>48</v>
-      </c>
-      <c r="S17" t="s">
-        <v>315</v>
-      </c>
-      <c r="T17">
-        <v>1.9E-3</v>
-      </c>
-      <c r="U17" t="s">
-        <v>48</v>
-      </c>
-      <c r="V17" t="s">
-        <v>316</v>
-      </c>
-      <c r="W17" t="s">
-        <v>48</v>
-      </c>
-      <c r="X17" t="s">
-        <v>317</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>318</v>
-      </c>
-      <c r="Z17">
-        <v>1.0800000000000001E-2</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF17">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>88</v>
-      </c>
-      <c r="AH17" t="s">
-        <v>319</v>
-      </c>
-      <c r="AI17" t="s">
-        <v>48</v>
-      </c>
-      <c r="AJ17">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>292</v>
-      </c>
-      <c r="B18" t="s">
-        <v>293</v>
-      </c>
-      <c r="C18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" t="s">
-        <v>320</v>
-      </c>
-      <c r="E18" t="s">
-        <v>321</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18" t="s">
-        <v>320</v>
-      </c>
-      <c r="H18" t="s">
-        <v>321</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>322</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
         <v>323</v>
       </c>
-      <c r="L18" t="s">
+      <c r="M18" t="s">
         <v>324</v>
-      </c>
-      <c r="M18">
-        <v>0.34410000000000002</v>
       </c>
       <c r="N18" t="s">
         <v>325</v>
       </c>
       <c r="O18" t="s">
+        <v>231</v>
+      </c>
+      <c r="P18" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q18">
+        <v>1.9E-3</v>
+      </c>
+      <c r="R18" t="s">
         <v>326</v>
       </c>
-      <c r="P18" t="s">
+      <c r="S18" t="s">
         <v>327</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="T18" t="s">
+        <v>91</v>
+      </c>
+      <c r="U18" t="s">
         <v>328</v>
       </c>
-      <c r="R18" t="s">
-        <v>234</v>
-      </c>
-      <c r="S18" t="s">
-        <v>251</v>
-      </c>
-      <c r="T18">
+      <c r="V18" t="s">
+        <v>329</v>
+      </c>
+      <c r="W18">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="X18" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>330</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>331</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>332</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>333</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>289</v>
+      </c>
+      <c r="B19" t="s">
+        <v>290</v>
+      </c>
+      <c r="C19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" t="s">
+        <v>334</v>
+      </c>
+      <c r="E19" t="s">
+        <v>335</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19" t="s">
+        <v>127</v>
+      </c>
+      <c r="H19" t="s">
+        <v>336</v>
+      </c>
+      <c r="I19" t="s">
+        <v>337</v>
+      </c>
+      <c r="J19">
+        <v>0.34410000000000002</v>
+      </c>
+      <c r="K19" t="s">
+        <v>338</v>
+      </c>
+      <c r="L19" t="s">
+        <v>339</v>
+      </c>
+      <c r="M19" t="s">
+        <v>131</v>
+      </c>
+      <c r="N19" t="s">
+        <v>311</v>
+      </c>
+      <c r="O19" t="s">
+        <v>45</v>
+      </c>
+      <c r="P19" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q19">
         <v>1.9E-3</v>
       </c>
-      <c r="U18" t="s">
-        <v>329</v>
-      </c>
-      <c r="V18" t="s">
-        <v>330</v>
-      </c>
-      <c r="W18" t="s">
-        <v>94</v>
-      </c>
-      <c r="X18" t="s">
-        <v>331</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>332</v>
-      </c>
-      <c r="Z18">
+      <c r="R19" t="s">
+        <v>340</v>
+      </c>
+      <c r="S19" t="s">
+        <v>341</v>
+      </c>
+      <c r="T19" t="s">
+        <v>45</v>
+      </c>
+      <c r="U19" t="s">
+        <v>342</v>
+      </c>
+      <c r="V19" t="s">
+        <v>343</v>
+      </c>
+      <c r="W19">
         <v>1.0800000000000001E-2</v>
       </c>
-      <c r="AA18" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB18" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>333</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE18" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF18">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>334</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>335</v>
-      </c>
-      <c r="AI18" t="s">
-        <v>336</v>
-      </c>
-      <c r="AJ18">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="s">
-        <v>60</v>
+      <c r="X19" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>344</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>236</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>208</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>345</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>292</v>
-      </c>
-      <c r="B19" t="s">
-        <v>293</v>
-      </c>
-      <c r="C19" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" t="s">
-        <v>337</v>
-      </c>
-      <c r="E19" t="s">
-        <v>338</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19" t="s">
-        <v>337</v>
-      </c>
-      <c r="H19" t="s">
-        <v>338</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19" t="s">
-        <v>130</v>
-      </c>
-      <c r="K19" t="s">
-        <v>339</v>
-      </c>
-      <c r="L19" t="s">
-        <v>340</v>
-      </c>
-      <c r="M19">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>289</v>
+      </c>
+      <c r="B20" t="s">
+        <v>290</v>
+      </c>
+      <c r="C20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" t="s">
+        <v>346</v>
+      </c>
+      <c r="E20" t="s">
+        <v>347</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20" t="s">
+        <v>348</v>
+      </c>
+      <c r="H20" t="s">
+        <v>349</v>
+      </c>
+      <c r="I20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J20">
         <v>0.34410000000000002</v>
       </c>
-      <c r="N19" t="s">
-        <v>341</v>
-      </c>
-      <c r="O19" t="s">
-        <v>342</v>
-      </c>
-      <c r="P19" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>314</v>
-      </c>
-      <c r="R19" t="s">
-        <v>48</v>
-      </c>
-      <c r="S19" t="s">
-        <v>136</v>
-      </c>
-      <c r="T19">
+      <c r="K20" t="s">
+        <v>351</v>
+      </c>
+      <c r="L20" t="s">
+        <v>352</v>
+      </c>
+      <c r="M20" t="s">
+        <v>219</v>
+      </c>
+      <c r="N20" t="s">
+        <v>353</v>
+      </c>
+      <c r="O20" t="s">
+        <v>195</v>
+      </c>
+      <c r="P20" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q20">
         <v>1.9E-3</v>
       </c>
-      <c r="U19" t="s">
-        <v>343</v>
-      </c>
-      <c r="V19" t="s">
-        <v>344</v>
-      </c>
-      <c r="W19" t="s">
-        <v>48</v>
-      </c>
-      <c r="X19" t="s">
-        <v>345</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>346</v>
-      </c>
-      <c r="Z19">
+      <c r="R20" t="s">
+        <v>355</v>
+      </c>
+      <c r="S20" t="s">
+        <v>356</v>
+      </c>
+      <c r="T20" t="s">
+        <v>45</v>
+      </c>
+      <c r="U20" t="s">
+        <v>199</v>
+      </c>
+      <c r="V20" t="s">
+        <v>315</v>
+      </c>
+      <c r="W20">
         <v>1.0800000000000001E-2</v>
       </c>
-      <c r="AA19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>347</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF19">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>239</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>211</v>
-      </c>
-      <c r="AI19" t="s">
-        <v>348</v>
-      </c>
-      <c r="AJ19">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="s">
-        <v>60</v>
+      <c r="X20" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>236</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>357</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>358</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>292</v>
-      </c>
-      <c r="B20" t="s">
-        <v>293</v>
-      </c>
-      <c r="C20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" t="s">
-        <v>349</v>
-      </c>
-      <c r="E20" t="s">
-        <v>350</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20" t="s">
-        <v>349</v>
-      </c>
-      <c r="H20" t="s">
-        <v>350</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20" t="s">
-        <v>351</v>
-      </c>
-      <c r="K20" t="s">
-        <v>352</v>
-      </c>
-      <c r="L20" t="s">
-        <v>353</v>
-      </c>
-      <c r="M20">
-        <v>0.34410000000000002</v>
-      </c>
-      <c r="N20" t="s">
-        <v>354</v>
-      </c>
-      <c r="O20" t="s">
-        <v>355</v>
-      </c>
-      <c r="P20" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>356</v>
-      </c>
-      <c r="R20" t="s">
-        <v>198</v>
-      </c>
-      <c r="S20" t="s">
-        <v>357</v>
-      </c>
-      <c r="T20">
-        <v>1.9E-3</v>
-      </c>
-      <c r="U20" t="s">
-        <v>358</v>
-      </c>
-      <c r="V20" t="s">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>359</v>
       </c>
-      <c r="W20" t="s">
-        <v>48</v>
-      </c>
-      <c r="X20" t="s">
-        <v>202</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>318</v>
-      </c>
-      <c r="Z20">
-        <v>1.0800000000000001E-2</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE20" t="s">
-        <v>124</v>
-      </c>
-      <c r="AF20">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>239</v>
-      </c>
-      <c r="AH20" t="s">
+      <c r="B21" t="s">
         <v>360</v>
       </c>
-      <c r="AI20" t="s">
+      <c r="C21" t="s">
         <v>361</v>
       </c>
-      <c r="AJ20">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="D21" t="s">
         <v>362</v>
       </c>
-      <c r="B21" t="s">
+      <c r="E21" t="s">
         <v>363</v>
       </c>
-      <c r="C21" t="s">
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21" t="s">
         <v>364</v>
       </c>
-      <c r="D21" t="s">
+      <c r="H21" t="s">
+        <v>294</v>
+      </c>
+      <c r="I21" t="s">
         <v>365</v>
       </c>
-      <c r="E21" t="s">
+      <c r="J21">
+        <v>2.92E-2</v>
+      </c>
+      <c r="K21" t="s">
         <v>366</v>
       </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21" t="s">
-        <v>365</v>
-      </c>
-      <c r="H21" t="s">
-        <v>366</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="L21" t="s">
+        <v>42</v>
+      </c>
+      <c r="M21" t="s">
         <v>367</v>
       </c>
-      <c r="K21" t="s">
-        <v>297</v>
-      </c>
-      <c r="L21" t="s">
+      <c r="N21" t="s">
         <v>368</v>
       </c>
-      <c r="M21">
-        <v>2.92E-2</v>
-      </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
+        <v>195</v>
+      </c>
+      <c r="P21" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q21">
+        <v>3.3E-3</v>
+      </c>
+      <c r="R21" t="s">
         <v>369</v>
       </c>
-      <c r="O21" t="s">
-        <v>45</v>
-      </c>
-      <c r="P21" t="s">
+      <c r="S21" t="s">
         <v>370</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="T21" t="s">
+        <v>45</v>
+      </c>
+      <c r="U21" t="s">
         <v>371</v>
       </c>
-      <c r="R21" t="s">
-        <v>198</v>
-      </c>
-      <c r="S21" t="s">
-        <v>199</v>
-      </c>
-      <c r="T21">
-        <v>3.3E-3</v>
-      </c>
-      <c r="U21" t="s">
+      <c r="V21" t="s">
         <v>372</v>
       </c>
-      <c r="V21" t="s">
+      <c r="W21">
+        <v>0.2044</v>
+      </c>
+      <c r="X21" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y21" t="s">
         <v>373</v>
       </c>
-      <c r="W21" t="s">
-        <v>48</v>
-      </c>
-      <c r="X21" t="s">
+      <c r="Z21" t="s">
         <v>374</v>
       </c>
-      <c r="Y21" t="s">
+      <c r="AA21" t="s">
         <v>375</v>
-      </c>
-      <c r="Z21">
-        <v>0.2044</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>204</v>
       </c>
       <c r="AB21" t="s">
         <v>376</v>
       </c>
-      <c r="AC21" t="s">
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="s">
         <v>377</v>
       </c>
-      <c r="AD21" t="s">
+      <c r="AE21" t="s">
         <v>378</v>
       </c>
-      <c r="AE21" t="s">
+      <c r="AF21" t="s">
         <v>379</v>
       </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="s">
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>359</v>
+      </c>
+      <c r="B22" t="s">
+        <v>360</v>
+      </c>
+      <c r="C22" t="s">
         <v>380</v>
       </c>
-      <c r="AH21" t="s">
+      <c r="D22" t="s">
         <v>381</v>
       </c>
-      <c r="AI21" t="s">
+      <c r="E22" t="s">
         <v>382</v>
       </c>
-      <c r="AJ21">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>362</v>
-      </c>
-      <c r="B22" t="s">
-        <v>363</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22" t="s">
+        <v>348</v>
+      </c>
+      <c r="H22" t="s">
         <v>383</v>
       </c>
-      <c r="D22" t="s">
+      <c r="I22" t="s">
+        <v>190</v>
+      </c>
+      <c r="J22">
+        <v>2.92E-2</v>
+      </c>
+      <c r="K22" t="s">
+        <v>351</v>
+      </c>
+      <c r="L22" t="s">
+        <v>192</v>
+      </c>
+      <c r="M22" t="s">
         <v>384</v>
       </c>
-      <c r="E22" t="s">
+      <c r="N22" t="s">
         <v>385</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22" t="s">
-        <v>384</v>
-      </c>
-      <c r="H22" t="s">
-        <v>385</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22" t="s">
-        <v>351</v>
-      </c>
-      <c r="K22" t="s">
-        <v>386</v>
-      </c>
-      <c r="L22" t="s">
-        <v>193</v>
-      </c>
-      <c r="M22">
-        <v>2.92E-2</v>
-      </c>
-      <c r="N22" t="s">
-        <v>354</v>
       </c>
       <c r="O22" t="s">
         <v>195</v>
       </c>
       <c r="P22" t="s">
+        <v>386</v>
+      </c>
+      <c r="Q22">
+        <v>3.3E-3</v>
+      </c>
+      <c r="R22" t="s">
+        <v>197</v>
+      </c>
+      <c r="S22" t="s">
         <v>387</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="T22" t="s">
+        <v>45</v>
+      </c>
+      <c r="U22" t="s">
+        <v>301</v>
+      </c>
+      <c r="V22" t="s">
         <v>388</v>
       </c>
-      <c r="R22" t="s">
-        <v>198</v>
-      </c>
-      <c r="S22" t="s">
+      <c r="W22">
+        <v>0.2044</v>
+      </c>
+      <c r="X22" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z22" t="s">
         <v>389</v>
       </c>
-      <c r="T22">
+      <c r="AA22" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>182</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>390</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>189</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>391</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>359</v>
+      </c>
+      <c r="B23" t="s">
+        <v>360</v>
+      </c>
+      <c r="C23" t="s">
+        <v>392</v>
+      </c>
+      <c r="D23" t="s">
+        <v>334</v>
+      </c>
+      <c r="E23" t="s">
+        <v>393</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23" t="s">
+        <v>308</v>
+      </c>
+      <c r="H23" t="s">
+        <v>140</v>
+      </c>
+      <c r="I23" t="s">
+        <v>394</v>
+      </c>
+      <c r="J23">
+        <v>2.92E-2</v>
+      </c>
+      <c r="K23" t="s">
+        <v>130</v>
+      </c>
+      <c r="L23" t="s">
+        <v>259</v>
+      </c>
+      <c r="M23" t="s">
+        <v>236</v>
+      </c>
+      <c r="N23" t="s">
+        <v>311</v>
+      </c>
+      <c r="O23" t="s">
+        <v>45</v>
+      </c>
+      <c r="P23" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q23">
         <v>3.3E-3</v>
       </c>
-      <c r="U22" t="s">
-        <v>200</v>
-      </c>
-      <c r="V22" t="s">
-        <v>390</v>
-      </c>
-      <c r="W22" t="s">
-        <v>48</v>
-      </c>
-      <c r="X22" t="s">
+      <c r="R23" t="s">
+        <v>395</v>
+      </c>
+      <c r="S23" t="s">
+        <v>396</v>
+      </c>
+      <c r="T23" t="s">
+        <v>45</v>
+      </c>
+      <c r="U23" t="s">
+        <v>342</v>
+      </c>
+      <c r="V23" t="s">
+        <v>397</v>
+      </c>
+      <c r="W23">
+        <v>0.2044</v>
+      </c>
+      <c r="X23" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>398</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>399</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="s">
         <v>304</v>
       </c>
-      <c r="Y22" t="s">
-        <v>391</v>
-      </c>
-      <c r="Z22">
-        <v>0.2044</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>204</v>
-      </c>
-      <c r="AB22" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC22" t="s">
-        <v>392</v>
-      </c>
-      <c r="AD22" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE22" t="s">
-        <v>185</v>
-      </c>
-      <c r="AF22">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>393</v>
-      </c>
-      <c r="AH22" t="s">
-        <v>192</v>
-      </c>
-      <c r="AI22" t="s">
-        <v>394</v>
-      </c>
-      <c r="AJ22">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="s">
-        <v>60</v>
+      <c r="AE23" t="s">
+        <v>316</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>362</v>
-      </c>
-      <c r="B23" t="s">
-        <v>363</v>
-      </c>
-      <c r="C23" t="s">
-        <v>395</v>
-      </c>
-      <c r="D23" t="s">
-        <v>337</v>
-      </c>
-      <c r="E23" t="s">
-        <v>396</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23" t="s">
-        <v>337</v>
-      </c>
-      <c r="H23" t="s">
-        <v>396</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23" t="s">
-        <v>311</v>
-      </c>
-      <c r="K23" t="s">
-        <v>143</v>
-      </c>
-      <c r="L23" t="s">
-        <v>397</v>
-      </c>
-      <c r="M23">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>359</v>
+      </c>
+      <c r="B24" t="s">
+        <v>360</v>
+      </c>
+      <c r="C24" t="s">
+        <v>400</v>
+      </c>
+      <c r="D24" t="s">
+        <v>401</v>
+      </c>
+      <c r="E24" t="s">
+        <v>402</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24" t="s">
+        <v>403</v>
+      </c>
+      <c r="H24" t="s">
+        <v>404</v>
+      </c>
+      <c r="I24" t="s">
+        <v>405</v>
+      </c>
+      <c r="J24">
         <v>2.92E-2</v>
       </c>
-      <c r="N23" t="s">
-        <v>133</v>
-      </c>
-      <c r="O23" t="s">
-        <v>262</v>
-      </c>
-      <c r="P23" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>314</v>
-      </c>
-      <c r="R23" t="s">
-        <v>48</v>
-      </c>
-      <c r="S23" t="s">
-        <v>271</v>
-      </c>
-      <c r="T23">
-        <v>3.3E-3</v>
-      </c>
-      <c r="U23" t="s">
-        <v>398</v>
-      </c>
-      <c r="V23" t="s">
-        <v>399</v>
-      </c>
-      <c r="W23" t="s">
-        <v>48</v>
-      </c>
-      <c r="X23" t="s">
-        <v>345</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>400</v>
-      </c>
-      <c r="Z23">
-        <v>0.2044</v>
-      </c>
-      <c r="AA23" t="s">
-        <v>139</v>
-      </c>
-      <c r="AB23" t="s">
-        <v>401</v>
-      </c>
-      <c r="AC23" t="s">
-        <v>402</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE23" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF23">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>307</v>
-      </c>
-      <c r="AH23" t="s">
-        <v>319</v>
-      </c>
-      <c r="AI23" t="s">
-        <v>48</v>
-      </c>
-      <c r="AJ23">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>362</v>
-      </c>
-      <c r="B24" t="s">
-        <v>363</v>
-      </c>
-      <c r="C24" t="s">
-        <v>403</v>
-      </c>
-      <c r="D24" t="s">
-        <v>404</v>
-      </c>
-      <c r="E24" t="s">
-        <v>405</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24" t="s">
-        <v>404</v>
-      </c>
-      <c r="H24" t="s">
-        <v>405</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>406</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
         <v>407</v>
       </c>
-      <c r="L24" t="s">
+      <c r="M24" t="s">
         <v>408</v>
-      </c>
-      <c r="M24">
-        <v>2.92E-2</v>
       </c>
       <c r="N24" t="s">
         <v>409</v>
       </c>
       <c r="O24" t="s">
+        <v>195</v>
+      </c>
+      <c r="P24" t="s">
         <v>410</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24">
+        <v>3.3E-3</v>
+      </c>
+      <c r="R24" t="s">
         <v>411</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="S24" t="s">
         <v>412</v>
       </c>
-      <c r="R24" t="s">
-        <v>198</v>
-      </c>
-      <c r="S24" t="s">
+      <c r="T24" t="s">
+        <v>91</v>
+      </c>
+      <c r="U24" t="s">
         <v>413</v>
       </c>
-      <c r="T24">
-        <v>3.3E-3</v>
-      </c>
-      <c r="U24" t="s">
+      <c r="V24" t="s">
         <v>414</v>
       </c>
-      <c r="V24" t="s">
+      <c r="W24">
+        <v>0.2044</v>
+      </c>
+      <c r="X24" t="s">
         <v>415</v>
       </c>
-      <c r="W24" t="s">
-        <v>94</v>
-      </c>
-      <c r="X24" t="s">
+      <c r="Y24" t="s">
+        <v>285</v>
+      </c>
+      <c r="Z24" t="s">
         <v>416</v>
       </c>
-      <c r="Y24" t="s">
+      <c r="AA24" t="s">
+        <v>375</v>
+      </c>
+      <c r="AB24" t="s">
         <v>417</v>
       </c>
-      <c r="Z24">
-        <v>0.2044</v>
-      </c>
-      <c r="AA24" t="s">
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>287</v>
+      </c>
+      <c r="AE24" t="s">
         <v>418</v>
       </c>
-      <c r="AB24" t="s">
-        <v>288</v>
-      </c>
-      <c r="AC24" t="s">
+      <c r="AF24" t="s">
         <v>419</v>
       </c>
-      <c r="AD24" t="s">
-        <v>378</v>
-      </c>
-      <c r="AE24" t="s">
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>359</v>
+      </c>
+      <c r="B25" t="s">
+        <v>360</v>
+      </c>
+      <c r="C25" t="s">
         <v>420</v>
       </c>
-      <c r="AF24">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>290</v>
-      </c>
-      <c r="AH24" t="s">
+      <c r="D25" t="s">
         <v>421</v>
       </c>
-      <c r="AI24" t="s">
+      <c r="E25" t="s">
         <v>422</v>
       </c>
-      <c r="AJ24">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>362</v>
-      </c>
-      <c r="B25" t="s">
-        <v>363</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" t="s">
+        <v>364</v>
+      </c>
+      <c r="H25" t="s">
         <v>423</v>
       </c>
-      <c r="D25" t="s">
+      <c r="I25" t="s">
         <v>424</v>
       </c>
-      <c r="E25" t="s">
+      <c r="J25">
+        <v>2.92E-2</v>
+      </c>
+      <c r="K25" t="s">
         <v>425</v>
       </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25" t="s">
-        <v>424</v>
-      </c>
-      <c r="H25" t="s">
-        <v>425</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25" t="s">
-        <v>367</v>
-      </c>
-      <c r="K25" t="s">
+      <c r="L25" t="s">
         <v>426</v>
       </c>
-      <c r="L25" t="s">
+      <c r="M25" t="s">
         <v>427</v>
-      </c>
-      <c r="M25">
-        <v>2.92E-2</v>
       </c>
       <c r="N25" t="s">
         <v>428</v>
       </c>
       <c r="O25" t="s">
+        <v>87</v>
+      </c>
+      <c r="P25" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q25">
+        <v>3.3E-3</v>
+      </c>
+      <c r="R25" t="s">
         <v>429</v>
       </c>
-      <c r="P25" t="s">
+      <c r="S25" t="s">
         <v>430</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="T25" t="s">
+        <v>45</v>
+      </c>
+      <c r="U25" t="s">
+        <v>371</v>
+      </c>
+      <c r="V25" t="s">
         <v>431</v>
       </c>
-      <c r="R25" t="s">
-        <v>90</v>
-      </c>
-      <c r="S25" t="s">
-        <v>286</v>
-      </c>
-      <c r="T25">
-        <v>3.3E-3</v>
-      </c>
-      <c r="U25" t="s">
+      <c r="W25">
+        <v>0.2044</v>
+      </c>
+      <c r="X25" t="s">
         <v>432</v>
       </c>
-      <c r="V25" t="s">
+      <c r="Y25" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z25" t="s">
         <v>433</v>
       </c>
-      <c r="W25" t="s">
-        <v>48</v>
-      </c>
-      <c r="X25" t="s">
-        <v>374</v>
-      </c>
-      <c r="Y25" t="s">
+      <c r="AA25" t="s">
         <v>434</v>
       </c>
-      <c r="Z25">
-        <v>0.2044</v>
-      </c>
-      <c r="AA25" t="s">
+      <c r="AB25" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>367</v>
+      </c>
+      <c r="AE25" t="s">
         <v>435</v>
       </c>
-      <c r="AB25" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC25" t="s">
+      <c r="AF25" t="s">
+        <v>391</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>436</v>
       </c>
-      <c r="AD25" t="s">
+      <c r="B26" t="s">
         <v>437</v>
       </c>
-      <c r="AE25" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF25">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>370</v>
-      </c>
-      <c r="AH25" t="s">
+      <c r="C26" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" t="s">
         <v>438</v>
       </c>
-      <c r="AI25" t="s">
-        <v>394</v>
-      </c>
-      <c r="AJ25">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="E26" t="s">
         <v>439</v>
-      </c>
-      <c r="B26" t="s">
-        <v>440</v>
-      </c>
-      <c r="C26" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" t="s">
-        <v>441</v>
-      </c>
-      <c r="E26" t="s">
-        <v>442</v>
       </c>
       <c r="F26">
         <v>0.57220000000000004</v>
       </c>
       <c r="G26" t="s">
+        <v>440</v>
+      </c>
+      <c r="H26" t="s">
+        <v>45</v>
+      </c>
+      <c r="I26" t="s">
+        <v>45</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" t="s">
         <v>441</v>
       </c>
-      <c r="H26" t="s">
+      <c r="L26" t="s">
         <v>442</v>
       </c>
-      <c r="I26">
-        <v>0.57220000000000004</v>
-      </c>
-      <c r="J26" t="s">
+      <c r="M26" t="s">
+        <v>367</v>
+      </c>
+      <c r="N26" t="s">
+        <v>353</v>
+      </c>
+      <c r="O26" t="s">
+        <v>45</v>
+      </c>
+      <c r="P26" t="s">
         <v>443</v>
       </c>
-      <c r="K26" t="s">
-        <v>48</v>
-      </c>
-      <c r="L26" t="s">
-        <v>48</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26" t="s">
+      <c r="Q26">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="R26" t="s">
         <v>444</v>
       </c>
-      <c r="O26" t="s">
+      <c r="S26" t="s">
+        <v>356</v>
+      </c>
+      <c r="T26" t="s">
+        <v>91</v>
+      </c>
+      <c r="U26" t="s">
         <v>445</v>
       </c>
-      <c r="P26" t="s">
-        <v>370</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>356</v>
-      </c>
-      <c r="R26" t="s">
-        <v>48</v>
-      </c>
-      <c r="S26" t="s">
+      <c r="V26" t="s">
         <v>446</v>
       </c>
-      <c r="T26">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="U26" t="s">
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26" t="s">
         <v>447</v>
       </c>
-      <c r="V26" t="s">
-        <v>359</v>
-      </c>
-      <c r="W26" t="s">
-        <v>94</v>
-      </c>
-      <c r="X26" t="s">
+      <c r="Y26" t="s">
+        <v>179</v>
+      </c>
+      <c r="Z26" t="s">
         <v>448</v>
       </c>
-      <c r="Y26" t="s">
+      <c r="AA26" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB26" t="s">
         <v>449</v>
       </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="s">
+      <c r="AC26">
+        <v>0.34410000000000002</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>172</v>
+      </c>
+      <c r="AE26" t="s">
         <v>450</v>
       </c>
-      <c r="AB26" t="s">
-        <v>182</v>
-      </c>
-      <c r="AC26" t="s">
+      <c r="AF26" t="s">
+        <v>206</v>
+      </c>
+      <c r="AG26">
+        <v>0.12889999999999999</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>436</v>
+      </c>
+      <c r="B27" t="s">
+        <v>437</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" t="s">
         <v>451</v>
       </c>
-      <c r="AD26" t="s">
-        <v>57</v>
-      </c>
-      <c r="AE26" t="s">
+      <c r="E27" t="s">
         <v>452</v>
-      </c>
-      <c r="AF26">
-        <v>0.34410000000000002</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>175</v>
-      </c>
-      <c r="AH26" t="s">
-        <v>453</v>
-      </c>
-      <c r="AI26" t="s">
-        <v>209</v>
-      </c>
-      <c r="AJ26">
-        <v>0.12889999999999999</v>
-      </c>
-      <c r="AK26" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>439</v>
-      </c>
-      <c r="B27" t="s">
-        <v>440</v>
-      </c>
-      <c r="C27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" t="s">
-        <v>454</v>
-      </c>
-      <c r="E27" t="s">
-        <v>455</v>
       </c>
       <c r="F27">
         <v>0.57220000000000004</v>
       </c>
       <c r="G27" t="s">
+        <v>45</v>
+      </c>
+      <c r="H27" t="s">
+        <v>77</v>
+      </c>
+      <c r="I27" t="s">
+        <v>45</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27" t="s">
+        <v>453</v>
+      </c>
+      <c r="L27" t="s">
+        <v>426</v>
+      </c>
+      <c r="M27" t="s">
         <v>454</v>
       </c>
-      <c r="H27" t="s">
+      <c r="N27" t="s">
+        <v>409</v>
+      </c>
+      <c r="O27" t="s">
         <v>455</v>
       </c>
-      <c r="I27">
-        <v>0.57220000000000004</v>
-      </c>
-      <c r="J27" t="s">
-        <v>48</v>
-      </c>
-      <c r="K27" t="s">
-        <v>80</v>
-      </c>
-      <c r="L27" t="s">
-        <v>48</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27" t="s">
+      <c r="P27" t="s">
         <v>456</v>
       </c>
-      <c r="O27" t="s">
-        <v>429</v>
-      </c>
-      <c r="P27" t="s">
+      <c r="Q27">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="R27" t="s">
         <v>457</v>
       </c>
-      <c r="Q27" t="s">
-        <v>412</v>
-      </c>
-      <c r="R27" t="s">
+      <c r="S27" t="s">
         <v>458</v>
       </c>
-      <c r="S27" t="s">
+      <c r="T27" t="s">
+        <v>45</v>
+      </c>
+      <c r="U27" t="s">
         <v>459</v>
       </c>
-      <c r="T27">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="U27" t="s">
+      <c r="V27" t="s">
         <v>460</v>
       </c>
-      <c r="V27" t="s">
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27" t="s">
         <v>461</v>
       </c>
-      <c r="W27" t="s">
-        <v>48</v>
-      </c>
-      <c r="X27" t="s">
+      <c r="Y27" t="s">
+        <v>179</v>
+      </c>
+      <c r="Z27" t="s">
         <v>462</v>
       </c>
-      <c r="Y27" t="s">
+      <c r="AA27" t="s">
         <v>463</v>
       </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="s">
+      <c r="AB27" t="s">
         <v>464</v>
       </c>
-      <c r="AB27" t="s">
-        <v>182</v>
-      </c>
-      <c r="AC27" t="s">
+      <c r="AC27">
+        <v>0.34410000000000002</v>
+      </c>
+      <c r="AD27" t="s">
         <v>465</v>
       </c>
-      <c r="AD27" t="s">
+      <c r="AE27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF27" t="s">
         <v>466</v>
       </c>
-      <c r="AE27" t="s">
+      <c r="AG27">
+        <v>0.12889999999999999</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>436</v>
+      </c>
+      <c r="B28" t="s">
+        <v>437</v>
+      </c>
+      <c r="C28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" t="s">
         <v>467</v>
       </c>
-      <c r="AF27">
-        <v>0.34410000000000002</v>
-      </c>
-      <c r="AG27" t="s">
+      <c r="E28" t="s">
         <v>468</v>
-      </c>
-      <c r="AH27" t="s">
-        <v>64</v>
-      </c>
-      <c r="AI27" t="s">
-        <v>469</v>
-      </c>
-      <c r="AJ27">
-        <v>0.12889999999999999</v>
-      </c>
-      <c r="AK27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>439</v>
-      </c>
-      <c r="B28" t="s">
-        <v>440</v>
-      </c>
-      <c r="C28" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" t="s">
-        <v>470</v>
-      </c>
-      <c r="E28" t="s">
-        <v>471</v>
       </c>
       <c r="F28">
         <v>0.57220000000000004</v>
       </c>
       <c r="G28" t="s">
+        <v>45</v>
+      </c>
+      <c r="H28" t="s">
+        <v>45</v>
+      </c>
+      <c r="I28" t="s">
+        <v>469</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" t="s">
         <v>470</v>
       </c>
-      <c r="H28" t="s">
+      <c r="L28" t="s">
         <v>471</v>
       </c>
-      <c r="I28">
-        <v>0.57220000000000004</v>
-      </c>
-      <c r="J28" t="s">
-        <v>48</v>
-      </c>
-      <c r="K28" t="s">
-        <v>48</v>
-      </c>
-      <c r="L28" t="s">
+      <c r="M28" t="s">
         <v>472</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
       </c>
       <c r="N28" t="s">
         <v>473</v>
@@ -5150,416 +4867,371 @@
       <c r="P28" t="s">
         <v>475</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="Q28">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="R28" t="s">
         <v>476</v>
       </c>
-      <c r="R28" t="s">
+      <c r="S28" t="s">
         <v>477</v>
       </c>
-      <c r="S28" t="s">
+      <c r="T28" t="s">
+        <v>45</v>
+      </c>
+      <c r="U28" t="s">
         <v>478</v>
       </c>
-      <c r="T28">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="U28" t="s">
+      <c r="V28" t="s">
         <v>479</v>
       </c>
-      <c r="V28" t="s">
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28" t="s">
         <v>480</v>
       </c>
-      <c r="W28" t="s">
-        <v>48</v>
-      </c>
-      <c r="X28" t="s">
+      <c r="Y28" t="s">
+        <v>251</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>416</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>375</v>
+      </c>
+      <c r="AB28" t="s">
         <v>481</v>
       </c>
-      <c r="Y28" t="s">
+      <c r="AC28">
+        <v>0.34410000000000002</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>472</v>
+      </c>
+      <c r="AE28" t="s">
         <v>482</v>
       </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="s">
+      <c r="AF28" t="s">
+        <v>238</v>
+      </c>
+      <c r="AG28">
+        <v>0.12889999999999999</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>483</v>
       </c>
-      <c r="AB28" t="s">
-        <v>254</v>
-      </c>
-      <c r="AC28" t="s">
-        <v>419</v>
-      </c>
-      <c r="AD28" t="s">
-        <v>378</v>
-      </c>
-      <c r="AE28" t="s">
+      <c r="B29" t="s">
         <v>484</v>
       </c>
-      <c r="AF28">
-        <v>0.34410000000000002</v>
-      </c>
-      <c r="AG28" t="s">
-        <v>475</v>
-      </c>
-      <c r="AH28" t="s">
+      <c r="C29" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" t="s">
         <v>485</v>
       </c>
-      <c r="AI28" t="s">
-        <v>241</v>
-      </c>
-      <c r="AJ28">
-        <v>0.12889999999999999</v>
-      </c>
-      <c r="AK28" t="s">
-        <v>60</v>
+      <c r="E29" t="s">
+        <v>45</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" t="s">
+        <v>486</v>
+      </c>
+      <c r="H29" t="s">
+        <v>487</v>
+      </c>
+      <c r="I29" t="s">
+        <v>488</v>
+      </c>
+      <c r="J29">
+        <v>0.57220000000000004</v>
+      </c>
+      <c r="K29" t="s">
+        <v>489</v>
+      </c>
+      <c r="L29" t="s">
+        <v>490</v>
+      </c>
+      <c r="M29" t="s">
+        <v>491</v>
+      </c>
+      <c r="N29" t="s">
+        <v>492</v>
+      </c>
+      <c r="O29" t="s">
+        <v>474</v>
+      </c>
+      <c r="P29" t="s">
+        <v>493</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29" t="s">
+        <v>457</v>
+      </c>
+      <c r="S29" t="s">
+        <v>494</v>
+      </c>
+      <c r="T29" t="s">
+        <v>91</v>
+      </c>
+      <c r="U29" t="s">
+        <v>71</v>
+      </c>
+      <c r="V29" t="s">
+        <v>495</v>
+      </c>
+      <c r="W29">
+        <v>0.82289999999999996</v>
+      </c>
+      <c r="X29" t="s">
+        <v>496</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>497</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>498</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>499</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>500</v>
+      </c>
+      <c r="AE29" t="s">
+        <v>482</v>
+      </c>
+      <c r="AF29" t="s">
+        <v>501</v>
+      </c>
+      <c r="AG29">
+        <v>0.45479999999999998</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>486</v>
-      </c>
-      <c r="B29" t="s">
-        <v>487</v>
-      </c>
-      <c r="C29" t="s">
-        <v>488</v>
-      </c>
-      <c r="D29" t="s">
-        <v>489</v>
-      </c>
-      <c r="E29" t="s">
-        <v>48</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29" t="s">
-        <v>489</v>
-      </c>
-      <c r="H29" t="s">
-        <v>48</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29" t="s">
-        <v>490</v>
-      </c>
-      <c r="K29" t="s">
-        <v>491</v>
-      </c>
-      <c r="L29" t="s">
-        <v>492</v>
-      </c>
-      <c r="M29">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>483</v>
+      </c>
+      <c r="B30" t="s">
+        <v>484</v>
+      </c>
+      <c r="C30" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" t="s">
+        <v>502</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30" t="s">
+        <v>503</v>
+      </c>
+      <c r="H30" t="s">
+        <v>504</v>
+      </c>
+      <c r="I30" t="s">
+        <v>505</v>
+      </c>
+      <c r="J30">
         <v>0.57220000000000004</v>
       </c>
-      <c r="N29" t="s">
-        <v>493</v>
-      </c>
-      <c r="O29" t="s">
-        <v>494</v>
-      </c>
-      <c r="P29" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>496</v>
-      </c>
-      <c r="R29" t="s">
-        <v>477</v>
-      </c>
-      <c r="S29" t="s">
-        <v>497</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29" t="s">
-        <v>460</v>
-      </c>
-      <c r="V29" t="s">
-        <v>498</v>
-      </c>
-      <c r="W29" t="s">
-        <v>94</v>
-      </c>
-      <c r="X29" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y29" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z29">
+      <c r="K30" t="s">
+        <v>441</v>
+      </c>
+      <c r="L30" t="s">
+        <v>407</v>
+      </c>
+      <c r="M30" t="s">
+        <v>65</v>
+      </c>
+      <c r="N30" t="s">
+        <v>152</v>
+      </c>
+      <c r="O30" t="s">
+        <v>455</v>
+      </c>
+      <c r="P30" t="s">
+        <v>506</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30" t="s">
+        <v>507</v>
+      </c>
+      <c r="S30" t="s">
+        <v>508</v>
+      </c>
+      <c r="T30" t="s">
+        <v>45</v>
+      </c>
+      <c r="U30" t="s">
+        <v>509</v>
+      </c>
+      <c r="V30" t="s">
+        <v>510</v>
+      </c>
+      <c r="W30">
         <v>0.82289999999999996</v>
       </c>
-      <c r="AA29" t="s">
-        <v>500</v>
-      </c>
-      <c r="AB29" t="s">
-        <v>501</v>
-      </c>
-      <c r="AC29" t="s">
-        <v>502</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE29" t="s">
-        <v>503</v>
-      </c>
-      <c r="AF29">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="s">
-        <v>504</v>
-      </c>
-      <c r="AH29" t="s">
-        <v>485</v>
-      </c>
-      <c r="AI29" t="s">
-        <v>505</v>
-      </c>
-      <c r="AJ29">
+      <c r="X30" t="s">
+        <v>511</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>373</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>512</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>463</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>513</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>514</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>515</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>516</v>
+      </c>
+      <c r="AG30">
         <v>0.45479999999999998</v>
       </c>
-      <c r="AK29" t="s">
-        <v>60</v>
+      <c r="AH30" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>486</v>
-      </c>
-      <c r="B30" t="s">
-        <v>487</v>
-      </c>
-      <c r="C30" t="s">
-        <v>506</v>
-      </c>
-      <c r="D30" t="s">
-        <v>48</v>
-      </c>
-      <c r="E30" t="s">
-        <v>507</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30" t="s">
-        <v>48</v>
-      </c>
-      <c r="H30" t="s">
-        <v>507</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30" t="s">
-        <v>508</v>
-      </c>
-      <c r="K30" t="s">
-        <v>509</v>
-      </c>
-      <c r="L30" t="s">
-        <v>510</v>
-      </c>
-      <c r="M30">
-        <v>0.57220000000000004</v>
-      </c>
-      <c r="N30" t="s">
-        <v>444</v>
-      </c>
-      <c r="O30" t="s">
-        <v>410</v>
-      </c>
-      <c r="P30" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>155</v>
-      </c>
-      <c r="R30" t="s">
-        <v>458</v>
-      </c>
-      <c r="S30" t="s">
-        <v>511</v>
-      </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
-      <c r="U30" t="s">
-        <v>512</v>
-      </c>
-      <c r="V30" t="s">
-        <v>513</v>
-      </c>
-      <c r="W30" t="s">
-        <v>48</v>
-      </c>
-      <c r="X30" t="s">
-        <v>514</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>515</v>
-      </c>
-      <c r="Z30">
-        <v>0.82289999999999996</v>
-      </c>
-      <c r="AA30" t="s">
-        <v>516</v>
-      </c>
-      <c r="AB30" t="s">
-        <v>376</v>
-      </c>
-      <c r="AC30" t="s">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>517</v>
       </c>
-      <c r="AD30" t="s">
-        <v>466</v>
-      </c>
-      <c r="AE30" t="s">
+      <c r="B31" t="s">
         <v>518</v>
       </c>
-      <c r="AF30">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="s">
+      <c r="D31" t="s">
         <v>519</v>
       </c>
-      <c r="AH30" t="s">
+      <c r="E31" t="s">
         <v>520</v>
-      </c>
-      <c r="AI30" t="s">
-        <v>521</v>
-      </c>
-      <c r="AJ30">
-        <v>0.45479999999999998</v>
-      </c>
-      <c r="AK30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>522</v>
-      </c>
-      <c r="B31" t="s">
-        <v>523</v>
-      </c>
-      <c r="D31" t="s">
-        <v>524</v>
-      </c>
-      <c r="E31" t="s">
-        <v>525</v>
       </c>
       <c r="F31">
         <v>0.45329999999999998</v>
       </c>
       <c r="G31" t="s">
+        <v>521</v>
+      </c>
+      <c r="H31" t="s">
+        <v>522</v>
+      </c>
+      <c r="I31" t="s">
+        <v>523</v>
+      </c>
+      <c r="J31">
+        <v>0.1986</v>
+      </c>
+      <c r="K31" t="s">
         <v>524</v>
       </c>
-      <c r="H31" t="s">
+      <c r="L31" t="s">
         <v>525</v>
       </c>
-      <c r="I31">
-        <v>0.45329999999999998</v>
-      </c>
-      <c r="J31" t="s">
+      <c r="M31" t="s">
         <v>526</v>
       </c>
-      <c r="K31" t="s">
+      <c r="N31" t="s">
         <v>527</v>
       </c>
-      <c r="L31" t="s">
+      <c r="O31" t="s">
         <v>528</v>
       </c>
-      <c r="M31">
-        <v>0.1986</v>
-      </c>
-      <c r="N31" t="s">
+      <c r="P31" t="s">
         <v>529</v>
       </c>
-      <c r="O31" t="s">
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31" t="s">
         <v>530</v>
       </c>
-      <c r="P31" t="s">
+      <c r="S31" t="s">
         <v>531</v>
       </c>
-      <c r="Q31" t="s">
+      <c r="T31" t="s">
         <v>532</v>
       </c>
-      <c r="R31" t="s">
+      <c r="U31" t="s">
         <v>533</v>
       </c>
-      <c r="S31" t="s">
+      <c r="V31" t="s">
         <v>534</v>
       </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31" t="s">
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31" t="s">
         <v>535</v>
       </c>
-      <c r="V31" t="s">
+      <c r="Y31" t="s">
         <v>536</v>
       </c>
-      <c r="W31" t="s">
+      <c r="Z31" t="s">
         <v>537</v>
       </c>
-      <c r="X31" t="s">
+      <c r="AA31" t="s">
         <v>538</v>
       </c>
-      <c r="Y31" t="s">
+      <c r="AB31" t="s">
         <v>539</v>
       </c>
-      <c r="Z31">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="s">
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="s">
         <v>540</v>
       </c>
-      <c r="AB31" t="s">
+      <c r="AE31" t="s">
         <v>541</v>
       </c>
-      <c r="AC31" t="s">
+      <c r="AF31" t="s">
         <v>542</v>
       </c>
-      <c r="AD31" t="s">
-        <v>543</v>
-      </c>
-      <c r="AE31" t="s">
-        <v>544</v>
-      </c>
-      <c r="AF31">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="s">
-        <v>545</v>
+      <c r="AG31">
+        <v>0</v>
       </c>
       <c r="AH31" t="s">
-        <v>546</v>
-      </c>
-      <c r="AI31" t="s">
-        <v>547</v>
-      </c>
-      <c r="AJ31">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C69BB14D-0316-457B-8B2E-A661D5AC8FDC}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>